--- a/SID/strategy-test-vault/v2.1-default-30d-timeout/SID V2.1 Method Back Testing.xlsx
+++ b/SID/strategy-test-vault/v2.1-default-30d-timeout/SID V2.1 Method Back Testing.xlsx
@@ -16,7 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategy Rules (V2.1)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Tiers" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Trades (V2.1 sized)'!$A$4:$Z$433</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Per-Ticker Summary'!$A$3:$H$111</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -32,7 +35,7 @@
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="+#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +68,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001F4E78"/>
     </font>
     <font>
       <b val="1"/>
@@ -130,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,19 +161,24 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -918,33 +931,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z433"/>
+  <dimension ref="A1:Z435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
@@ -42534,7 +42547,116 @@
         <v>46109.15</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL (filtered)</t>
+        </is>
+      </c>
+      <c r="B434" s="16" t="n"/>
+      <c r="C434" s="16" t="n"/>
+      <c r="D434" s="16" t="n"/>
+      <c r="E434" s="16" t="n"/>
+      <c r="F434" s="16" t="n"/>
+      <c r="G434" s="17">
+        <f>SUBTOTAL(9,G5:G433)</f>
+        <v/>
+      </c>
+      <c r="H434" s="18">
+        <f>SUBTOTAL(9,H5:H433)</f>
+        <v/>
+      </c>
+      <c r="I434" s="16" t="n"/>
+      <c r="J434" s="16" t="n"/>
+      <c r="K434" s="18">
+        <f>SUBTOTAL(9,K5:K433)</f>
+        <v/>
+      </c>
+      <c r="L434" s="16" t="n"/>
+      <c r="M434" s="16" t="n"/>
+      <c r="N434" s="16" t="n"/>
+      <c r="O434" s="16" t="n"/>
+      <c r="P434" s="16" t="n"/>
+      <c r="Q434" s="17">
+        <f>SUBTOTAL(9,Q5:Q433)</f>
+        <v/>
+      </c>
+      <c r="R434" s="19">
+        <f>SUBTOTAL(9,R5:R433)</f>
+        <v/>
+      </c>
+      <c r="S434" s="16" t="n"/>
+      <c r="T434" s="16" t="n"/>
+      <c r="U434" s="16" t="n"/>
+      <c r="V434" s="17">
+        <f>SUBTOTAL(9,V5:V433)</f>
+        <v/>
+      </c>
+      <c r="W434" s="19">
+        <f>SUBTOTAL(9,W5:W433)</f>
+        <v/>
+      </c>
+      <c r="X434" s="19">
+        <f>SUBTOTAL(9,X5:X433)</f>
+        <v/>
+      </c>
+      <c r="Y434" s="16" t="n"/>
+      <c r="Z434" s="16" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="20" t="inlineStr">
+        <is>
+          <t>FILTER STATS:</t>
+        </is>
+      </c>
+      <c r="B435" s="21" t="inlineStr">
+        <is>
+          <t>Trades:</t>
+        </is>
+      </c>
+      <c r="C435" s="21">
+        <f>SUBTOTAL(2,A5:A433)</f>
+        <v/>
+      </c>
+      <c r="D435" s="21" t="inlineStr">
+        <is>
+          <t>Wins:</t>
+        </is>
+      </c>
+      <c r="E435" s="21">
+        <f>SUMPRODUCT(SUBTOTAL(3,OFFSET(Y5,ROW(Y5:Y433)-ROW(Y5),0,1))*(Y5:Y433="WIN"))</f>
+        <v/>
+      </c>
+      <c r="F435" s="21" t="inlineStr">
+        <is>
+          <t>Win Rate %:</t>
+        </is>
+      </c>
+      <c r="G435" s="22">
+        <f>IFERROR(E435/C435*100,0)</f>
+        <v/>
+      </c>
+      <c r="H435" s="21" t="inlineStr">
+        <is>
+          <t>Avg P&amp;L:</t>
+        </is>
+      </c>
+      <c r="I435" s="23">
+        <f>IFERROR(SUBTOTAL(9,X5:X433)/C435,0)</f>
+        <v/>
+      </c>
+      <c r="J435" s="21" t="inlineStr">
+        <is>
+          <t>Net P&amp;L $:</t>
+        </is>
+      </c>
+      <c r="K435" s="23">
+        <f>SUBTOTAL(9,X5:X433)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:Z433"/>
   <mergeCells count="2">
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A2:Z2"/>
@@ -42553,13 +42675,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42627,7 +42749,7 @@
       <c r="D4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F4" s="11" t="n">
@@ -42655,7 +42777,7 @@
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F5" s="11" t="n">
@@ -42683,7 +42805,7 @@
       <c r="D6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="24" t="n">
         <v>85.71428571428571</v>
       </c>
       <c r="F6" s="11" t="n">
@@ -42711,7 +42833,7 @@
       <c r="D7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F7" s="11" t="n">
@@ -42739,7 +42861,7 @@
       <c r="D8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F8" s="11" t="n">
@@ -42767,7 +42889,7 @@
       <c r="D9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="24" t="n">
         <v>57.14285714285714</v>
       </c>
       <c r="F9" s="11" t="n">
@@ -42795,7 +42917,7 @@
       <c r="D10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="24" t="n">
         <v>57.14285714285714</v>
       </c>
       <c r="F10" s="11" t="n">
@@ -42823,7 +42945,7 @@
       <c r="D11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F11" s="11" t="n">
@@ -42851,7 +42973,7 @@
       <c r="D12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="24" t="n">
         <v>80</v>
       </c>
       <c r="F12" s="11" t="n">
@@ -42879,7 +43001,7 @@
       <c r="D13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F13" s="11" t="n">
@@ -42907,7 +43029,7 @@
       <c r="D14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="24" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="F14" s="11" t="n">
@@ -42935,7 +43057,7 @@
       <c r="D15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F15" s="11" t="n">
@@ -42963,7 +43085,7 @@
       <c r="D16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F16" s="11" t="n">
@@ -42991,7 +43113,7 @@
       <c r="D17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F17" s="11" t="n">
@@ -43019,7 +43141,7 @@
       <c r="D18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F18" s="11" t="n">
@@ -43047,7 +43169,7 @@
       <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F19" s="11" t="n">
@@ -43075,7 +43197,7 @@
       <c r="D20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="24" t="n">
         <v>60</v>
       </c>
       <c r="F20" s="11" t="n">
@@ -43103,7 +43225,7 @@
       <c r="D21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F21" s="11" t="n">
@@ -43131,7 +43253,7 @@
       <c r="D22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F22" s="11" t="n">
@@ -43159,7 +43281,7 @@
       <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F23" s="11" t="n">
@@ -43187,7 +43309,7 @@
       <c r="D24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="24" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="F24" s="11" t="n">
@@ -43215,7 +43337,7 @@
       <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="24" t="n">
         <v>80</v>
       </c>
       <c r="F25" s="11" t="n">
@@ -43243,7 +43365,7 @@
       <c r="D26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="24" t="n">
         <v>40</v>
       </c>
       <c r="F26" s="11" t="n">
@@ -43271,7 +43393,7 @@
       <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F27" s="11" t="n">
@@ -43299,7 +43421,7 @@
       <c r="D28" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="24" t="n">
         <v>40</v>
       </c>
       <c r="F28" s="11" t="n">
@@ -43327,7 +43449,7 @@
       <c r="D29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F29" s="11" t="n">
@@ -43355,7 +43477,7 @@
       <c r="D30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F30" s="11" t="n">
@@ -43383,7 +43505,7 @@
       <c r="D31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="24" t="n">
         <v>75</v>
       </c>
       <c r="F31" s="11" t="n">
@@ -43411,7 +43533,7 @@
       <c r="D32" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F32" s="11" t="n">
@@ -43439,7 +43561,7 @@
       <c r="D33" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="24" t="n">
         <v>75</v>
       </c>
       <c r="F33" s="11" t="n">
@@ -43467,7 +43589,7 @@
       <c r="D34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F34" s="11" t="n">
@@ -43495,7 +43617,7 @@
       <c r="D35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F35" s="11" t="n">
@@ -43523,7 +43645,7 @@
       <c r="D36" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="24" t="n">
         <v>57.14285714285714</v>
       </c>
       <c r="F36" s="11" t="n">
@@ -43551,7 +43673,7 @@
       <c r="D37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="24" t="n">
         <v>80</v>
       </c>
       <c r="F37" s="11" t="n">
@@ -43579,7 +43701,7 @@
       <c r="D38" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="24" t="n">
         <v>75</v>
       </c>
       <c r="F38" s="11" t="n">
@@ -43607,7 +43729,7 @@
       <c r="D39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F39" s="11" t="n">
@@ -43635,7 +43757,7 @@
       <c r="D40" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="24" t="n">
         <v>50</v>
       </c>
       <c r="F40" s="11" t="n">
@@ -43663,7 +43785,7 @@
       <c r="D41" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="24" t="n">
         <v>40</v>
       </c>
       <c r="F41" s="11" t="n">
@@ -43691,7 +43813,7 @@
       <c r="D42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F42" s="11" t="n">
@@ -43719,7 +43841,7 @@
       <c r="D43" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="24" t="n">
         <v>71.42857142857143</v>
       </c>
       <c r="F43" s="11" t="n">
@@ -43747,7 +43869,7 @@
       <c r="D44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E44" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F44" s="11" t="n">
@@ -43775,7 +43897,7 @@
       <c r="D45" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="24" t="n">
         <v>71.42857142857143</v>
       </c>
       <c r="F45" s="11" t="n">
@@ -43803,7 +43925,7 @@
       <c r="D46" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="24" t="n">
         <v>75</v>
       </c>
       <c r="F46" s="11" t="n">
@@ -43831,7 +43953,7 @@
       <c r="D47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F47" s="11" t="n">
@@ -43859,7 +43981,7 @@
       <c r="D48" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="24" t="n">
         <v>60</v>
       </c>
       <c r="F48" s="11" t="n">
@@ -43887,7 +44009,7 @@
       <c r="D49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F49" s="11" t="n">
@@ -43915,7 +44037,7 @@
       <c r="D50" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F50" s="11" t="n">
@@ -43943,7 +44065,7 @@
       <c r="D51" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="24" t="n">
         <v>50</v>
       </c>
       <c r="F51" s="11" t="n">
@@ -43971,7 +44093,7 @@
       <c r="D52" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="E52" s="24" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="F52" s="11" t="n">
@@ -43999,7 +44121,7 @@
       <c r="D53" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E53" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F53" s="11" t="n">
@@ -44027,7 +44149,7 @@
       <c r="D54" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="E54" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F54" s="11" t="n">
@@ -44055,7 +44177,7 @@
       <c r="D55" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="24" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="F55" s="11" t="n">
@@ -44083,7 +44205,7 @@
       <c r="D56" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="E56" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F56" s="11" t="n">
@@ -44111,7 +44233,7 @@
       <c r="D57" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="E57" s="24" t="n">
         <v>75</v>
       </c>
       <c r="F57" s="11" t="n">
@@ -44139,7 +44261,7 @@
       <c r="D58" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="E58" s="24" t="n">
         <v>40</v>
       </c>
       <c r="F58" s="11" t="n">
@@ -44167,7 +44289,7 @@
       <c r="D59" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="E59" s="24" t="n">
         <v>50</v>
       </c>
       <c r="F59" s="11" t="n">
@@ -44195,7 +44317,7 @@
       <c r="D60" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E60" s="16" t="n">
+      <c r="E60" s="24" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F60" s="11" t="n">
@@ -44223,7 +44345,7 @@
       <c r="D61" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="16" t="n">
+      <c r="E61" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F61" s="11" t="n">
@@ -44251,7 +44373,7 @@
       <c r="D62" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E62" s="16" t="n">
+      <c r="E62" s="24" t="n">
         <v>44.44444444444444</v>
       </c>
       <c r="F62" s="11" t="n">
@@ -44279,7 +44401,7 @@
       <c r="D63" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="16" t="n">
+      <c r="E63" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F63" s="11" t="n">
@@ -44307,7 +44429,7 @@
       <c r="D64" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E64" s="16" t="n">
+      <c r="E64" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F64" s="11" t="n">
@@ -44335,7 +44457,7 @@
       <c r="D65" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E65" s="16" t="n">
+      <c r="E65" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F65" s="11" t="n">
@@ -44363,7 +44485,7 @@
       <c r="D66" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="16" t="n">
+      <c r="E66" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F66" s="11" t="n">
@@ -44391,7 +44513,7 @@
       <c r="D67" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E67" s="16" t="n">
+      <c r="E67" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F67" s="11" t="n">
@@ -44419,7 +44541,7 @@
       <c r="D68" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E68" s="16" t="n">
+      <c r="E68" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F68" s="11" t="n">
@@ -44447,7 +44569,7 @@
       <c r="D69" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="16" t="n">
+      <c r="E69" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F69" s="11" t="n">
@@ -44475,7 +44597,7 @@
       <c r="D70" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E70" s="16" t="n">
+      <c r="E70" s="24" t="n">
         <v>25</v>
       </c>
       <c r="F70" s="11" t="n">
@@ -44503,7 +44625,7 @@
       <c r="D71" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E71" s="16" t="n">
+      <c r="E71" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F71" s="11" t="n">
@@ -44531,7 +44653,7 @@
       <c r="D72" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E72" s="16" t="n">
+      <c r="E72" s="24" t="n">
         <v>50</v>
       </c>
       <c r="F72" s="11" t="n">
@@ -44559,7 +44681,7 @@
       <c r="D73" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="16" t="n">
+      <c r="E73" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F73" s="11" t="n">
@@ -44587,7 +44709,7 @@
       <c r="D74" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E74" s="16" t="n">
+      <c r="E74" s="24" t="n">
         <v>50</v>
       </c>
       <c r="F74" s="11" t="n">
@@ -44615,7 +44737,7 @@
       <c r="D75" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E75" s="16" t="n">
+      <c r="E75" s="24" t="n">
         <v>50</v>
       </c>
       <c r="F75" s="11" t="n">
@@ -44643,7 +44765,7 @@
       <c r="D76" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E76" s="16" t="n">
+      <c r="E76" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F76" s="11" t="n">
@@ -44671,7 +44793,7 @@
       <c r="D77" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="16" t="n">
+      <c r="E77" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F77" s="11" t="n">
@@ -44699,7 +44821,7 @@
       <c r="D78" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="16" t="n">
+      <c r="E78" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F78" s="11" t="n">
@@ -44727,7 +44849,7 @@
       <c r="D79" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E79" s="16" t="n">
+      <c r="E79" s="24" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F79" s="11" t="n">
@@ -44755,7 +44877,7 @@
       <c r="D80" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E80" s="16" t="n">
+      <c r="E80" s="24" t="n">
         <v>50</v>
       </c>
       <c r="F80" s="11" t="n">
@@ -44783,7 +44905,7 @@
       <c r="D81" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E81" s="16" t="n">
+      <c r="E81" s="24" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F81" s="11" t="n">
@@ -44811,7 +44933,7 @@
       <c r="D82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E82" s="16" t="n">
+      <c r="E82" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F82" s="11" t="n">
@@ -44839,7 +44961,7 @@
       <c r="D83" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E83" s="17" t="n">
+      <c r="E83" s="25" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F83" s="13" t="n">
@@ -44867,7 +44989,7 @@
       <c r="D84" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E84" s="17" t="n">
+      <c r="E84" s="25" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F84" s="13" t="n">
@@ -44895,7 +45017,7 @@
       <c r="D85" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E85" s="17" t="n">
+      <c r="E85" s="25" t="n">
         <v>50</v>
       </c>
       <c r="F85" s="13" t="n">
@@ -44923,7 +45045,7 @@
       <c r="D86" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E86" s="17" t="n">
+      <c r="E86" s="25" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F86" s="13" t="n">
@@ -44951,7 +45073,7 @@
       <c r="D87" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E87" s="17" t="n">
+      <c r="E87" s="25" t="n">
         <v>50</v>
       </c>
       <c r="F87" s="13" t="n">
@@ -44979,7 +45101,7 @@
       <c r="D88" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E88" s="17" t="n">
+      <c r="E88" s="25" t="n">
         <v>40</v>
       </c>
       <c r="F88" s="13" t="n">
@@ -45007,7 +45129,7 @@
       <c r="D89" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E89" s="17" t="n">
+      <c r="E89" s="25" t="n">
         <v>50</v>
       </c>
       <c r="F89" s="13" t="n">
@@ -45035,7 +45157,7 @@
       <c r="D90" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E90" s="17" t="n">
+      <c r="E90" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="13" t="n">
@@ -45063,7 +45185,7 @@
       <c r="D91" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="17" t="n">
+      <c r="E91" s="25" t="n">
         <v>50</v>
       </c>
       <c r="F91" s="13" t="n">
@@ -45091,7 +45213,7 @@
       <c r="D92" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E92" s="17" t="n">
+      <c r="E92" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="13" t="n">
@@ -45119,7 +45241,7 @@
       <c r="D93" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E93" s="17" t="n">
+      <c r="E93" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F93" s="13" t="n">
@@ -45147,7 +45269,7 @@
       <c r="D94" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E94" s="17" t="n">
+      <c r="E94" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="13" t="n">
@@ -45175,7 +45297,7 @@
       <c r="D95" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E95" s="17" t="n">
+      <c r="E95" s="25" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F95" s="13" t="n">
@@ -45203,7 +45325,7 @@
       <c r="D96" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="17" t="n">
+      <c r="E96" s="25" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F96" s="13" t="n">
@@ -45231,7 +45353,7 @@
       <c r="D97" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E97" s="17" t="n">
+      <c r="E97" s="25" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F97" s="13" t="n">
@@ -45259,7 +45381,7 @@
       <c r="D98" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="17" t="n">
+      <c r="E98" s="25" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F98" s="13" t="n">
@@ -45287,7 +45409,7 @@
       <c r="D99" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E99" s="17" t="n">
+      <c r="E99" s="25" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F99" s="13" t="n">
@@ -45315,7 +45437,7 @@
       <c r="D100" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E100" s="17" t="n">
+      <c r="E100" s="25" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F100" s="13" t="n">
@@ -45343,7 +45465,7 @@
       <c r="D101" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E101" s="17" t="n">
+      <c r="E101" s="25" t="n">
         <v>66.66666666666666</v>
       </c>
       <c r="F101" s="13" t="n">
@@ -45371,7 +45493,7 @@
       <c r="D102" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E102" s="17" t="n">
+      <c r="E102" s="25" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F102" s="13" t="n">
@@ -45399,7 +45521,7 @@
       <c r="D103" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="17" t="n">
+      <c r="E103" s="25" t="n">
         <v>50</v>
       </c>
       <c r="F103" s="13" t="n">
@@ -45427,7 +45549,7 @@
       <c r="D104" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="E104" s="17" t="n">
+      <c r="E104" s="25" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="F104" s="13" t="n">
@@ -45455,7 +45577,7 @@
       <c r="D105" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E105" s="17" t="n">
+      <c r="E105" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="13" t="n">
@@ -45483,7 +45605,7 @@
       <c r="D106" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E106" s="17" t="n">
+      <c r="E106" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="13" t="n">
@@ -45511,7 +45633,7 @@
       <c r="D107" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E107" s="17" t="n">
+      <c r="E107" s="25" t="n">
         <v>40</v>
       </c>
       <c r="F107" s="13" t="n">
@@ -45539,7 +45661,7 @@
       <c r="D108" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E108" s="17" t="n">
+      <c r="E108" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="13" t="n">
@@ -45567,7 +45689,7 @@
       <c r="D109" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E109" s="17" t="n">
+      <c r="E109" s="25" t="n">
         <v>16.66666666666666</v>
       </c>
       <c r="F109" s="13" t="n">
@@ -45595,7 +45717,7 @@
       <c r="D110" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E110" s="17" t="n">
+      <c r="E110" s="25" t="n">
         <v>16.66666666666666</v>
       </c>
       <c r="F110" s="13" t="n">
@@ -45623,7 +45745,7 @@
       <c r="D111" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E111" s="17" t="n">
+      <c r="E111" s="25" t="n">
         <v>16.66666666666666</v>
       </c>
       <c r="F111" s="13" t="n">
@@ -45637,34 +45759,42 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B112" s="18" t="n">
-        <v>429</v>
-      </c>
-      <c r="C112" s="18" t="n">
-        <v>274</v>
-      </c>
-      <c r="D112" s="18" t="n">
-        <v>155</v>
-      </c>
-      <c r="E112" s="19" t="n">
-        <v>63.86946386946387</v>
-      </c>
-      <c r="F112" s="20" t="n">
-        <v>36109.15</v>
-      </c>
-      <c r="G112" s="20" t="n">
-        <v>84.17051282051283</v>
-      </c>
-      <c r="H112" s="18" t="n">
-        <v>10.8</v>
+      <c r="A112" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL (filtered)</t>
+        </is>
+      </c>
+      <c r="B112" s="16">
+        <f>SUBTOTAL(9,B4:B111)</f>
+        <v/>
+      </c>
+      <c r="C112" s="16">
+        <f>SUBTOTAL(9,C4:C111)</f>
+        <v/>
+      </c>
+      <c r="D112" s="16">
+        <f>SUBTOTAL(9,D4:D111)</f>
+        <v/>
+      </c>
+      <c r="E112" s="26">
+        <f>IFERROR(C112/B112*100,0)</f>
+        <v/>
+      </c>
+      <c r="F112" s="19">
+        <f>SUBTOTAL(9,F4:F111)</f>
+        <v/>
+      </c>
+      <c r="G112" s="19">
+        <f>IFERROR(F112/B112,0)</f>
+        <v/>
+      </c>
+      <c r="H112" s="26">
+        <f>IFERROR(SUBTOTAL(1,H4:H111),0)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H111"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -46151,7 +46281,7 @@
       <c r="D5" s="11" t="n">
         <v>3229.81</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="27" t="n">
         <v>0.322981</v>
       </c>
       <c r="F5" s="5" t="n">
@@ -46171,7 +46301,7 @@
       <c r="D6" s="11" t="n">
         <v>1825.75</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="27" t="n">
         <v>0.1380027377566269</v>
       </c>
       <c r="F6" s="5" t="n">
@@ -46191,7 +46321,7 @@
       <c r="D7" s="11" t="n">
         <v>7520.47</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="27" t="n">
         <v>0.4995144650879808</v>
       </c>
       <c r="F7" s="5" t="n">
@@ -46211,7 +46341,7 @@
       <c r="D8" s="11" t="n">
         <v>6757.93</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="27" t="n">
         <v>0.2993409381543168</v>
       </c>
       <c r="F8" s="5" t="n">
@@ -46231,7 +46361,7 @@
       <c r="D9" s="11" t="n">
         <v>7477.94</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="27" t="n">
         <v>0.2549243266166588</v>
       </c>
       <c r="F9" s="5" t="n">
@@ -46251,7 +46381,7 @@
       <c r="D10" s="11" t="n">
         <v>9297.25</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="27" t="n">
         <v>0.252560992505141</v>
       </c>
       <c r="F10" s="5" t="n">
@@ -46259,24 +46389,24 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="18" t="n">
         <v>46109.15</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="28" t="n">
         <v>36109.15</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="29" t="n">
         <v>3.610915</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="16" t="n">
         <v>429</v>
       </c>
     </row>
@@ -46368,7 +46498,7 @@
       <c r="B5" t="n">
         <v>161</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.579136690647482</v>
       </c>
       <c r="D5" s="10" t="n">
@@ -46397,7 +46527,7 @@
       <c r="B6" t="n">
         <v>32</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.1151079136690648</v>
       </c>
       <c r="D6" s="10" t="n">
@@ -46426,7 +46556,7 @@
       <c r="B7" t="n">
         <v>79</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.2841726618705036</v>
       </c>
       <c r="D7" s="10" t="n">
@@ -46455,7 +46585,7 @@
       <c r="B8" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.02158273381294964</v>
       </c>
       <c r="D8" s="10" t="n">
@@ -46476,29 +46606,29 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>ALL WINNERS</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="16" t="n">
         <v>278</v>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="32" t="n">
         <v>124.92</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="32" t="n">
         <v>34727.17</v>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Sum of TP2 leg P&amp;L across all 210 TP1 winners</t>
         </is>
       </c>
-      <c r="G9" s="18" t="n"/>
+      <c r="G9" s="16" t="n"/>
     </row>
     <row r="10"/>
     <row r="11"/>
@@ -46609,7 +46739,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Stage 1 — ARM (signal day)</t>
         </is>
@@ -46708,7 +46838,7 @@
       <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>Stage 2 — TRIGGER (entry day, 1-3 bars after arm)</t>
         </is>
@@ -46807,7 +46937,7 @@
       <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>Stage 3 — TP1 (NEW in V2.1)</t>
         </is>
@@ -46872,7 +47002,7 @@
       <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>Stage 4 — TP2 (NEW in V2.1, runner exits)</t>
         </is>
@@ -46954,7 +47084,7 @@
       <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>Position sizing</t>
         </is>
@@ -47019,7 +47149,7 @@
       <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>Universe &amp; tier routing</t>
         </is>
@@ -47178,24 +47308,24 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>COMBINED</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="16" t="n">
         <v>429</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="16" t="n">
         <v>108</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="16" t="n">
         <v>63.9</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="32" t="n">
         <v>36109.15</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="32" t="n">
         <v>84.17</v>
       </c>
     </row>
